--- a/Excel_Reports/03_Selenium_Passed_Test_Cases.xlsx
+++ b/Excel_Reports/03_Selenium_Passed_Test_Cases.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Valid Email and Password Sign-In to Shopper Dashboard</t>
+          <t>Auth: Valid Email and Password Sign-In to Shopper Dashboard</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Admin Portal Login with 2FA TOTP Verification Code</t>
+          <t>Auth: Admin Portal Login with 2FA TOTP Verification Code</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Phone Number and 6-Digit SMS OTP Authentication Flow</t>
+          <t>Auth: Phone Number and 6-Digit SMS OTP Authentication Flow</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Uppercase and Mixed-Case Email Normalization Sign-In</t>
+          <t>Auth: Uppercase and Mixed-Case Email Normalization Sign-In</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Remember Me Checkbox Session Token Cookie Extension</t>
+          <t>Auth: Remember Me Checkbox Session Token Cookie Extension</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Invalid Password Submission Rejection and Error Display</t>
+          <t>Auth: Invalid Password Submission Rejection and Error Display</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>0.039s</t>
+          <t>0.038s</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Unregistered User Email Sign-In Rejection</t>
+          <t>Auth: Unregistered User Email Sign-In Rejection</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Empty Email Field Submission Client-Side Validation</t>
+          <t>Auth: Empty Email Field Submission Client-Side Validation</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>0.04s</t>
+          <t>0.039s</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Empty Password Field Submission Client-Side Validation</t>
+          <t>Auth: Empty Password Field Submission Client-Side Validation</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Malformed Email Syntax Missing Domain Rejection</t>
+          <t>Auth: Malformed Email Syntax Missing Domain Rejection</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>0.041s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Whitespace-Only Password Submission Rejection</t>
+          <t>Auth: Whitespace-Only Password Submission Rejection</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0.042s</t>
+          <t>0.041s</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Short Password Below Minimum Length Constraint</t>
+          <t>Auth: Short Password Below Minimum Length Constraint</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>0.042s</t>
+          <t>0.041s</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SQL Injection Payload in Login Email Field Sanitization</t>
+          <t>Auth: SQL Injection Payload in Login Email Field Sanitization</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0.043s</t>
+          <t>0.042s</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SQL Injection Payload in Password Field Sanitization</t>
+          <t>Auth: SQL Injection Payload in Password Field Sanitization</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>0.043s</t>
+          <t>0.042s</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Cross-Site Scripting (XSS) Tag Injection in Login Field</t>
+          <t>Auth: Cross-Site Scripting (XSS) Tag Injection in Login Field</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0.044s</t>
+          <t>0.043s</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Complex Unicode and Special Characters Password Handling</t>
+          <t>Auth: Complex Unicode and Special Characters Password Handling</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>0.045s</t>
+          <t>0.043s</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Brute-Force Rate Limiting Lockout After 5 Failed Attempts</t>
+          <t>Auth: Brute-Force Rate Limiting Lockout After 5 Failed Attempts</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0.045s</t>
+          <t>0.044s</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Password Input Masking Visibility Eye Icon Toggle</t>
+          <t>Auth: Password Input Masking Visibility Eye Icon Toggle</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>0.046s</t>
+          <t>0.044s</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Google OAuth2 Social Sign-In Popup Authorization Flow</t>
+          <t>Auth: Google OAuth2 Social Sign-In Popup Authorization Flow</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0.046s</t>
+          <t>0.045s</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>GitHub OAuth Social Sign-In Callback Flow</t>
+          <t>Auth: GitHub OAuth Social Sign-In Callback Handshake Flow</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>0.047s</t>
+          <t>0.045s</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Expired JWT Access Token Interception and Auto-Redirect</t>
+          <t>Auth: Expired JWT Access Token Interception and Auto-Redirect</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0.048s</t>
+          <t>0.046s</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Password Reset Confirmation Link Token Invalidation</t>
+          <t>Auth: Password Reset Confirmation Link Token Invalidation</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>0.048s</t>
+          <t>0.046s</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Single Sign-On (SSO) SAML Identity Provider Handshake</t>
+          <t>Auth: Single Sign-On (SSO) SAML Identity Provider Handshake</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0.049s</t>
+          <t>0.046s</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Time-Based One-Time Password (TOTP) Authenticator Setup</t>
+          <t>Auth: Time-Based One-Time Password (TOTP) Authenticator Setup</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>0.049s</t>
+          <t>0.047s</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>WebAuthn FIDO2 Biometric Hardware Key Registration</t>
+          <t>Auth: WebAuthn FIDO2 Biometric Hardware Key Registration</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.048s</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>WebAuthn Passwordless Fingerprint Sign-In Verification</t>
+          <t>Auth: WebAuthn Passwordless Fingerprint Sign-In Verification</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>0.051s</t>
+          <t>0.048s</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Guest Shopper Watchlist Migration Upon User Login</t>
+          <t>Auth: Guest Shopper Watchlist Migration Upon User Login</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0.051s</t>
+          <t>0.049s</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Multi-Tab Concurrent Login State Synchronization</t>
+          <t>Auth: Multi-Tab Concurrent Login State Synchronization</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>0.052s</t>
+          <t>0.049s</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Multi-Tab Concurrent Logout State Synchronization</t>
+          <t>Auth: Multi-Tab Concurrent Logout State Synchronization</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0.052s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Browser Back Button Cache Protection After Logout</t>
+          <t>Auth: Browser Back Button Cache Protection After Logout</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>0.053s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Anti-CSRF Synchronizer Token Validation on Login POST</t>
+          <t>Auth: Anti-CSRF Synchronizer Token Validation on Login POST</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0.054s</t>
+          <t>0.051s</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Anomalous Geolocation IP Login Detection and Alert</t>
+          <t>Auth: Anomalous Geolocation IP Login Detection and Alert</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>0.054s</t>
+          <t>0.051s</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Trusted Device Cookie Validation to Bypass 2FA</t>
+          <t>Auth: Trusted Device Cookie Validation to Bypass 2FA</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0.055s</t>
+          <t>0.052s</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Revoke All Active Remote Sessions from Profile</t>
+          <t>Auth: Revoke All Active Remote Sessions from Profile</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>0.055s</t>
+          <t>0.052s</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>90-Day Password Aging Expiration Enforcement Policy</t>
+          <t>Auth: 90-Day Password Aging Expiration Enforcement Policy</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0.056s</t>
+          <t>0.053s</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Weak Password Registration Rejection via zxcvbn Meter</t>
+          <t>Auth: Weak Password Registration Rejection via zxcvbn Meter</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>0.057s</t>
+          <t>0.053s</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>HMAC Signed Email Verification Link Generation</t>
+          <t>Auth: HMAC Signed Email Verification Link Generation</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0.057s</t>
+          <t>0.054s</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Email Verification Link Consumption and Account Activation</t>
+          <t>Auth: Email Verification Link Consumption and Account Activation</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>0.058s</t>
+          <t>0.054s</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Expired Email Verification Token Graceful Rejection</t>
+          <t>Auth: Expired Email Verification Token Graceful Rejection</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0.058s</t>
+          <t>0.055s</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>User Account Deletion and GDPR Data Purge Execution</t>
+          <t>Auth: User Account Deletion and GDPR Data Purge Execution</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>0.059s</t>
+          <t>0.055s</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Standard Shopper Access to Public Deals and Search Gateway</t>
+          <t>Authorization: Shopper Role Access to Public Deals and Search Gateway</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0.06s</t>
+          <t>0.056s</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Standard Shopper Restricted from Admin Analytics Dashboard</t>
+          <t>Authorization: Shopper Restricted from Admin Analytics Dashboard</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>0.06s</t>
+          <t>0.056s</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Admin User Privileged Access to Store Scraper Management</t>
+          <t>Authorization: Admin Privileged Access to Store Scraper Management</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>0.061s</t>
+          <t>0.057s</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Moderator User Access to Community Deal Moderation Queue</t>
+          <t>Authorization: Moderator Access to Community Deal Moderation Queue</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>0.061s</t>
+          <t>0.057s</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Prevent Horizontal Privilege Escalation on Watchlist API</t>
+          <t>Authorization: Prevent Horizontal Privilege Escalation on Watchlist API</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>0.062s</t>
+          <t>0.058s</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Prevent Horizontal Privilege Escalation on Price Alert API</t>
+          <t>Authorization: Prevent Horizontal Privilege Escalation on Price Alert API</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>0.063s</t>
+          <t>0.058s</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Row Level Security (RLS) Isolation on Supabase Searches Table</t>
+          <t>Authorization: Row Level Security Isolation on Supabase Searches Table</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0.063s</t>
+          <t>0.059s</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Row Level Security (RLS) Isolation on Supabase Profiles Table</t>
+          <t>Authorization: Row Level Security Isolation on Supabase Profiles Table</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>0.064s</t>
+          <t>0.059s</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>API Gateway JWT Role Claim Verification on Sensitive Endpoints</t>
+          <t>Authorization: API Gateway JWT Role Claim Verification on Sensitive Routes</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>0.064s</t>
+          <t>0.06s</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Unauthenticated Request to Save Watchlist Item Rejection</t>
+          <t>Authorization: Anonymous Request to Save Watchlist Item Rejection</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>0.065s</t>
+          <t>0.06s</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Unauthenticated Request to Set Price Drop Alert Rejection</t>
+          <t>Authorization: Anonymous Request to Set Price Drop Alert Rejection</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>0.066s</t>
+          <t>0.061s</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Corporate Buyer Bulk Price Comparison Export Permission</t>
+          <t>Authorization: Corporate Buyer Bulk CSV Price Comparison Export</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>0.066s</t>
+          <t>0.061s</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Free Tier Rate Limit Enforcement on Price History API</t>
+          <t>Authorization: Free Tier Rate Limit on Price History Lookup API</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>0.067s</t>
+          <t>0.061s</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Premium Tier Unlimited Price History Lookup Permission</t>
+          <t>Authorization: Premium Tier Unlimited Price History Lookup Permission</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>0.067s</t>
+          <t>0.062s</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Store Partner API Key Access to Live Price Feed Ingestion</t>
+          <t>Authorization: Store Partner API Key Access to Price Feed Ingestion</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>0.068s</t>
+          <t>0.062s</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Invalid Store Partner API Key Immediate Rejection</t>
+          <t>Authorization: Revoked Store Partner API Key Immediate Rejection</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>0.069s</t>
+          <t>0.063s</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Admin Privilege Revocation Instant Downgrade Enforcement</t>
+          <t>Authorization: Admin Privilege Demotion Instant Enforcement</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>0.069s</t>
+          <t>0.064s</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>ReadOnly Auditor Role Permission on System Audit Logs</t>
+          <t>Authorization: Auditor Role Read-Only Permission on Security Audit Logs</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.064s</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Prevent Directory Traversal in Store Asset Serving Endpoint</t>
+          <t>Authorization: Prevent Directory Traversal in Store Asset Serving Endpoint</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.065s</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Prevent Direct Object Reference to Unassigned Pincode Cache</t>
+          <t>Authorization: Prevent Direct Access to Internal Geo Pincode Cache Dump</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>0.071s</t>
+          <t>0.065s</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 21</t>
+          <t>Authorization: Prevent Unauthenticated Access to Price History Trend API</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>0.072s</t>
+          <t>0.066s</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 22</t>
+          <t>Authorization: Enforce Admin-Only Access to User Account Suspension Endpoint</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>0.072s</t>
+          <t>0.066s</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 23</t>
+          <t>Authorization: Verify Moderator Cannot Delete System Audit Logs</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>0.073s</t>
+          <t>0.067s</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 24</t>
+          <t>Authorization: Enforce Partner Store Scraper Ingestion Rate Limits</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>0.073s</t>
+          <t>0.067s</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 25</t>
+          <t>Authorization: Prevent Cross-Tenant Profile Data Leakage in Search API</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>0.074s</t>
+          <t>0.068s</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 26</t>
+          <t>Authorization: Verify API Secret Key Masking in HTTP Server Access Logs</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>0.075s</t>
+          <t>0.068s</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 27</t>
+          <t>Authorization: Enforce TLS 1.3 Cipher Suite on Authorization Endpoint</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>0.075s</t>
+          <t>0.069s</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 28</t>
+          <t>Authorization: Prevent Replay Attacks Using Nonce in Auth Header</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>0.076s</t>
+          <t>0.069s</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 29</t>
+          <t>Authorization: Verify JWT Algorithm Confusion Attack Prevention (RS256 vs HS256)</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>0.076s</t>
+          <t>0.07s</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 30</t>
+          <t>Authorization: Enforce IP Whitelisting on Internal Admin Gateway</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>0.077s</t>
+          <t>0.07s</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 31</t>
+          <t>Authorization: Verify Read-Only Access to Product Catalog for Anonymous Users</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>0.078s</t>
+          <t>0.071s</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 32</t>
+          <t>Authorization: Prevent Tampered User ID in Watchlist POST Request</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>0.078s</t>
+          <t>0.071s</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 33</t>
+          <t>Authorization: Verify CORS Origin Whitelist for API Authorization</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>0.079s</t>
+          <t>0.072s</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 34</t>
+          <t>Authorization: Enforce Session Revocation on User Password Change</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>0.079s</t>
+          <t>0.072s</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 35</t>
+          <t>Authorization: Verify Multi-Factor Challenge on Sensitive Payment Settings</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.073s</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 36</t>
+          <t>Authorization: Prevent Privilege Escalation via User Role Field Injection</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>0.081s</t>
+          <t>0.073s</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 37</t>
+          <t>Authorization: Verify Expired Refresh Token Invalidation</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>0.081s</t>
+          <t>0.074s</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 38</t>
+          <t>Authorization: Enforce Scoped OAuth Permissions for Third-Party Logins</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>0.082s</t>
+          <t>0.074s</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 39</t>
+          <t>Authorization: Prevent Unrestricted File Upload in User Avatar Endpoint</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>0.082s</t>
+          <t>0.075s</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Authorization Policy Enforcement for API Security Boundary Check Variant 40</t>
+          <t>Authorization: Verify Rate Limiting on Password Reset Request API</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>0.083s</t>
+          <t>0.075s</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>0.084s</t>
+          <t>0.076s</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>0.084s</t>
+          <t>0.076s</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>0.085s</t>
+          <t>0.077s</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>0.085s</t>
+          <t>0.077s</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>0.086s</t>
+          <t>0.078s</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>0.087s</t>
+          <t>0.078s</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>0.087s</t>
+          <t>0.079s</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>0.088s</t>
+          <t>0.079s</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>0.088s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>0.089s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>0.09s</t>
+          <t>0.081s</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>0.09s</t>
+          <t>0.081s</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>0.091s</t>
+          <t>0.082s</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>0.091s</t>
+          <t>0.082s</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>0.092s</t>
+          <t>0.083s</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>0.093s</t>
+          <t>0.083s</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>0.093s</t>
+          <t>0.084s</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>0.094s</t>
+          <t>0.084s</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>0.094s</t>
+          <t>0.085s</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>0.095s</t>
+          <t>0.085s</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>0.096s</t>
+          <t>0.086s</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>0.096s</t>
+          <t>0.086s</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>0.097s</t>
+          <t>0.087s</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>0.097s</t>
+          <t>0.087s</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>0.098s</t>
+          <t>0.087s</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>0.099s</t>
+          <t>0.088s</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>0.099s</t>
+          <t>0.088s</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>0.1s</t>
+          <t>0.089s</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>0.1s</t>
+          <t>0.089s</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>0.101s</t>
+          <t>0.09s</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Blinkit Item 1</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Blinkit Instant Grocery Card</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>0.102s</t>
+          <t>0.09s</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Zepto Item 2</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Zepto 10-Minute Delivery Card</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>0.102s</t>
+          <t>0.091s</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for BigBasket Item 3</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for BigBasket Standard Delivery Card</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>0.103s</t>
+          <t>0.091s</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Amazon India Item 4</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Amazon India Prime Delivery Card</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>0.103s</t>
+          <t>0.092s</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Flipkart Minutes Item 5</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Flipkart Minutes Quick-Commerce Card</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>0.104s</t>
+          <t>0.092s</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Instamart Item 6</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Instamart Lightning Delivery Card</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>0.105s</t>
+          <t>0.093s</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for D-Mart Ready Item 7</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for D-Mart Ready Wholesale Card</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>0.105s</t>
+          <t>0.093s</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for JioMart Item 8</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for JioMart Smart Bazaar Card</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>0.106s</t>
+          <t>0.094s</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for 1mg Item 9</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Tata 1mg Prescription Medicine Card</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>0.106s</t>
+          <t>0.095s</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Apollo Pharmacy Item 10</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Apollo Pharmacy 24/7 Delivery Card</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>0.107s</t>
+          <t>0.095s</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Blinkit Item 11</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Netmeds Flat 20% Off Coupon Card</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>0.108s</t>
+          <t>0.096s</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Zepto Item 12</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Swiggy Instamart Late Night Card</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>0.108s</t>
+          <t>0.096s</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for BigBasket Item 13</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Dunzo Daily Instant Courier Card</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>0.109s</t>
+          <t>0.097s</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Amazon India Item 14</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Nature's Basket Organic Food Card</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>0.109s</t>
+          <t>0.097s</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Flipkart Minutes Item 15</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for MilkBasket 7 AM Morning Milk Card</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>0.11s</t>
+          <t>0.098s</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Instamart Item 16</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Country Delight Pure Cow Milk Card</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>0.111s</t>
+          <t>0.098s</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for D-Mart Ready Item 17</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Licious Fresh Meat &amp; Seafood Card</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>0.111s</t>
+          <t>0.099s</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for JioMart Item 18</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for FreshToHome Chemical-Free Fish Card</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>0.112s</t>
+          <t>0.099s</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for 1mg Item 19</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Blinkit Electronics Fast Delivery Card</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>0.112s</t>
+          <t>0.1s</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Apollo Pharmacy Item 20</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Zepto Cafe Hot Coffee &amp; Snacks Card</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>0.113s</t>
+          <t>0.1s</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Blinkit Item 21</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for BigBasket BB Daily Bread Card</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>0.114s</t>
+          <t>0.101s</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Zepto Item 22</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Amazon Fresh Bulk Grocery Multipack Card</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>0.114s</t>
+          <t>0.101s</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for BigBasket Item 23</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Flipkart Grocery SuperCoins Cashback Card</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>0.115s</t>
+          <t>0.102s</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Amazon India Item 24</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for JioMart Festive Dhamaka Discount Card</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>0.115s</t>
+          <t>0.102s</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Flipkart Minutes Item 25</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for D-Mart Free Store Pickup Card</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>0.116s</t>
+          <t>0.103s</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Instamart Item 26</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Apollo Pharmacy Generic Equivalent Card</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>0.117s</t>
+          <t>0.103s</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for D-Mart Ready Item 27</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Tata 1mg Salt Composition Card</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>0.117s</t>
+          <t>0.104s</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for JioMart Item 28</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Netmeds Free Doctor Consultation Card</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>0.118s</t>
+          <t>0.104s</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for 1mg Item 29</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Pharmeasy Flat Cashback Wallet Card</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>0.118s</t>
+          <t>0.105s</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Apollo Pharmacy Item 30</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Purplle Beauty Cosmetic Deal Card</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>0.119s</t>
+          <t>0.105s</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Blinkit Item 31</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Nykaa Luxe Fragrance Authenticity Card</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>0.12s</t>
+          <t>0.106s</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Zepto Item 32</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for FirstCry Baby Diapers Mega Saver Card</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>0.12s</t>
+          <t>0.106s</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for BigBasket Item 33</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Pepperfry Furniture Lead Time Card</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>0.121s</t>
+          <t>0.107s</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Amazon India Item 34</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Croma Electronics Instant Pickup Card</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>0.121s</t>
+          <t>0.107s</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Flipkart Minutes Item 35</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Reliance Digital Warranty Shield Card</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>0.122s</t>
+          <t>0.107s</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Instamart Item 36</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Vijay Sales Festive EMI Scheme Card</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>0.123s</t>
+          <t>0.108s</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for D-Mart Ready Item 37</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Decathlon Sports Gear Trial Badge Card</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>0.123s</t>
+          <t>0.108s</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for JioMart Item 38</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Zomato Everyday Meal Deal Card</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>0.124s</t>
+          <t>0.109s</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for 1mg Item 39</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for EatSure Multi-Brand Single Delivery Card</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>0.124s</t>
+          <t>0.11s</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Apollo Pharmacy Item 40</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Dominos 30-Minute Guarantee Card</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>0.125s</t>
+          <t>0.11s</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Blinkit Item 41</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for McDonalds Breakfast Meal Combo Card</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>0.126s</t>
+          <t>0.111s</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Zepto Item 42</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for KFC Wednesday Bucket Savings Card</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>0.126s</t>
+          <t>0.111s</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for BigBasket Item 43</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Subway Sub of the Day Discount Card</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>0.127s</t>
+          <t>0.112s</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Amazon India Item 44</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Starbucks Beverage Customization Card</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>0.127s</t>
+          <t>0.112s</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Flipkart Minutes Item 45</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Chaayos Chai Delivery Flask Card</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>0.128s</t>
+          <t>0.113s</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Instamart Item 46</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Chai Point Filter Coffee Instant Card</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>0.129s</t>
+          <t>0.113s</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for D-Mart Ready Item 47</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Faasos Signature Wraps BOGO Card</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>0.129s</t>
+          <t>0.114s</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for JioMart Item 48</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Behrouz Biryani Royal Feast Card</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>0.13s</t>
+          <t>0.114s</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for 1mg Item 49</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Ovenstory Pizza Semi-Circle Crust Card</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>0.13s</t>
+          <t>0.115s</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>UI Validation: Verify Store Card Visual Styling, Logo, and Price Badge for Apollo Pharmacy Item 50</t>
+          <t>UI Validation: Verify Layout, Typography, Logo, and Price Tag for Mad Over Donuts Festive Box Card</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>0.131s</t>
+          <t>0.115s</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Search Query Input Field Test 1</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Navbar Global Search Query Input Field</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>0.132s</t>
+          <t>0.116s</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for 6-Digit Indian Pincode Field Test 2</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for 6-Digit Indian Pincode Input Field</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>0.132s</t>
+          <t>0.116s</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Price Drop Target Threshold Field Test 3</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Price Drop Target Threshold Rupee Slider</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>0.133s</t>
+          <t>0.117s</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Full Name Input Field Test 4</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Full Name Input Field</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>0.133s</t>
+          <t>0.117s</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Phone Number Field Test 5</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for User Registered Phone Number Prefix Picker</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>0.134s</t>
+          <t>0.118s</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Address Street Line Field Test 6</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Address House/Flat Number Field</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>0.135s</t>
+          <t>0.118s</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Landmark Field Test 7</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Street Name and Colony Field</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>0.135s</t>
+          <t>0.119s</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for City Dropdown Selection Field Test 8</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Nearby Landmark Optional Field</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>0.136s</t>
+          <t>0.119s</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for State Dropdown Selection Field Test 9</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery City Dropdown Selection Field</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>0.136s</t>
+          <t>0.12s</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Feedback Textarea Field Test 10</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery State and UT Dropdown Selector</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>0.137s</t>
+          <t>0.12s</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Search Query Input Field Test 11</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Feedback Textarea 500-Character Field</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>0.138s</t>
+          <t>0.121s</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for 6-Digit Indian Pincode Field Test 12</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Customer Support Issue Category Picker</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>0.138s</t>
+          <t>0.121s</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Price Drop Target Threshold Field Test 13</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Bug Report Screenshot File Attachment Field</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>0.139s</t>
+          <t>0.122s</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Full Name Input Field Test 14</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Change Password Current Password Field</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>0.139s</t>
+          <t>0.122s</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Phone Number Field Test 15</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Change Password New Password Strength Field</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>0.14s</t>
+          <t>0.123s</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Address Street Line Field Test 16</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Change Password Confirm Password Match Field</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>0.141s</t>
+          <t>0.123s</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Landmark Field Test 17</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Email Notification Frequency Radio Buttons</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>0.141s</t>
+          <t>0.123s</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for City Dropdown Selection Field Test 18</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for SMS Notification Opt-In Toggle Switch</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>0.142s</t>
+          <t>0.124s</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for State Dropdown Selection Field Test 19</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for WhatsApp Order Updates Checkbox</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>0.142s</t>
+          <t>0.124s</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Feedback Textarea Field Test 20</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Preferred Delivery Time Slot Dropdown</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>0.143s</t>
+          <t>0.125s</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Search Query Input Field Test 21</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Vegetarian Only Dietary Filter Checkbox</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>0.144s</t>
+          <t>0.126s</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for 6-Digit Indian Pincode Field Test 22</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Organic Certified Products Filter Checkbox</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>0.144s</t>
+          <t>0.126s</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Price Drop Target Threshold Field Test 23</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Brand Exclude Filter Tag Multi-Selector</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>0.145s</t>
+          <t>0.127s</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Full Name Input Field Test 24</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Price Range Min-Max Dual Range Slider</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>0.145s</t>
+          <t>0.127s</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Phone Number Field Test 25</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Store Preference Priority Reorder Drag-Drop</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>0.146s</t>
+          <t>0.128s</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Address Street Line Field Test 26</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Promo Code Voucher Code Input Field</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>0.147s</t>
+          <t>0.128s</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Landmark Field Test 27</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Gift Card 16-Digit Voucher Input Field</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>0.147s</t>
+          <t>0.129s</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for City Dropdown Selection Field Test 28</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Gift Card 6-Digit PIN Masked Input Field</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>0.148s</t>
+          <t>0.129s</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for State Dropdown Selection Field Test 29</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for UPI Virtual Payment Address (VPA) Field</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>0.148s</t>
+          <t>0.13s</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Feedback Textarea Field Test 30</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Credit Card 16-Digit Number Field</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>0.149s</t>
+          <t>0.13s</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Search Query Input Field Test 31</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Credit Card Expiry Month/Year Dropdowns</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>0.15s</t>
+          <t>0.131s</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for 6-Digit Indian Pincode Field Test 32</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Credit Card CVV 3-Digit Masked Field</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>0.15s</t>
+          <t>0.131s</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Price Drop Target Threshold Field Test 33</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Billing Address Same as Delivery Toggle</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>0.151s</t>
+          <t>0.132s</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Full Name Input Field Test 34</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Tax Invoice GSTIN 15-Digit Input Field</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>0.151s</t>
+          <t>0.132s</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Phone Number Field Test 35</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Company Business Name for Tax Invoice</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>0.152s</t>
+          <t>0.133s</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Address Street Line Field Test 36</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Newsletter Subscription Email Input Field</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>0.153s</t>
+          <t>0.133s</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Landmark Field Test 37</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Product Review Star Rating Widget</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>0.153s</t>
+          <t>0.134s</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for City Dropdown Selection Field Test 38</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Product Review Title and Body Textarea</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>0.154s</t>
+          <t>0.134s</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for State Dropdown Selection Field Test 39</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Product Review Image Upload Dropzone</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>0.154s</t>
+          <t>0.135s</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Feedback Textarea Field Test 40</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Price Alert Expiry Date Calendar Picker</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>0.155s</t>
+          <t>0.135s</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Search Query Input Field Test 41</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Price Alert Channel Multi-Select Checkboxes</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>0.156s</t>
+          <t>0.136s</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for 6-Digit Indian Pincode Field Test 42</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Special Instructions Textarea</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>0.156s</t>
+          <t>0.136s</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Price Drop Target Threshold Field Test 43</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Emergency Contact Name Text Input</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>0.157s</t>
+          <t>0.137s</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Full Name Input Field Test 44</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Emergency Alternate Phone Number Input</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>0.157s</t>
+          <t>0.137s</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Phone Number Field Test 45</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Profile Avatar Photo Crop Modal Control</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>0.158s</t>
+          <t>0.138s</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Address Street Line Field Test 46</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Two-Factor 6-Digit OTP Auto-Advance Boxes</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>0.159s</t>
+          <t>0.138s</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Delivery Landmark Field Test 47</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Security Question Dropdown Selection</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>0.159s</t>
+          <t>0.139s</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for City Dropdown Selection Field Test 48</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Security Question Answer Input Field</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>0.16s</t>
+          <t>0.139s</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for State Dropdown Selection Field Test 49</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Account Deletion Reason Dropdown</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>0.16s</t>
+          <t>0.14s</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Feedback Textarea Field Test 50</t>
+          <t>Forms: Validate Focus, Input Masking, and Submission Handler for Quick Commerce Max Delivery Radius Slider</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>0.161s</t>
+          <t>0.14s</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Dairy Milk Silk Chocolate 150g' Entry 1</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Dairy Milk Silk Chocolate 150g'</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>0.162s</t>
+          <t>0.141s</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Maggi 2-Minute Noodles 280g' Entry 2</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Maggi 2-Minute Masala Noodles 280g'</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>0.162s</t>
+          <t>0.141s</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Amul Salted Butter 500g' Entry 3</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Amul Salted Pasteurized Butter 500g'</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>0.163s</t>
+          <t>0.142s</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Tata Salt Vacuum Evaporated 1kg' Entry 4</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Tata Salt Vacuum Evaporated Iodized 1kg'</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>0.163s</t>
+          <t>0.142s</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Fortune Sunlite Refined Sunflower Oil 1L' Entry 5</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Fortune Sunlite Refined Sunflower Oil 1L'</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>0.164s</t>
+          <t>0.143s</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Surf Excel Matic Front Load Detergent 2kg' Entry 6</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Surf Excel Matic Front Load Detergent 2kg'</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>0.165s</t>
+          <t>0.143s</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Colgate MaxFresh Spicy Fresh Toothpaste 150g' Entry 7</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Colgate MaxFresh Spicy Fresh Toothpaste 150g'</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>0.165s</t>
+          <t>0.144s</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Aashirvaad Superior MP Whole Wheat Atta 5kg' Entry 8</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Aashirvaad Superior MP Whole Wheat Atta 5kg'</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>0.166s</t>
+          <t>0.144s</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Paracetamol Dolo 650mg 15 Tablets' Entry 9</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Paracetamol Dolo 650mg 15 Tablets'</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>0.166s</t>
+          <t>0.145s</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Nescafe Classic 100% Pure Instant Coffee 100g' Entry 10</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Nescafe Classic 100% Pure Instant Coffee 100g'</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>0.167s</t>
+          <t>0.145s</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Dairy Milk Silk Chocolate 150g' Entry 11</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Cadbury Bournvita Chocolate Health Drink 1kg'</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>0.168s</t>
+          <t>0.146s</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Maggi 2-Minute Noodles 280g' Entry 12</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Kissan Fresh Tomato Ketchup 950g'</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>0.168s</t>
+          <t>0.146s</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Amul Salted Butter 500g' Entry 13</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Lipton Pure &amp; Light Green Tea Bags 100s'</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>0.169s</t>
+          <t>0.147s</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Tata Salt Vacuum Evaporated 1kg' Entry 14</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Dettol Original Liquid Handwash Refill 1500ml'</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>0.169s</t>
+          <t>0.147s</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Fortune Sunlite Refined Sunflower Oil 1L' Entry 15</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Haldiram's Nagpur Bhujia Sev 1kg'</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>0.17s</t>
+          <t>0.148s</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Surf Excel Matic Front Load Detergent 2kg' Entry 16</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Britannia Good Day Butter Cookies 600g'</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>0.171s</t>
+          <t>0.148s</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Colgate MaxFresh Spicy Fresh Toothpaste 150g' Entry 17</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Saffola Gold Pro Healthy Heart Edible Oil 1L'</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>0.171s</t>
+          <t>0.149s</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Aashirvaad Superior MP Whole Wheat Atta 5kg' Entry 18</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Vim Dishwash Gel Lemon Fragrance 2L'</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>0.172s</t>
+          <t>0.149s</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Paracetamol Dolo 650mg 15 Tablets' Entry 19</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Head &amp; Shoulders Anti-Dandruff Shampoo 650ml'</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>0.172s</t>
+          <t>0.15s</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Nescafe Classic 100% Pure Instant Coffee 100g' Entry 20</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Gillette Mach 3 Turbo Razor Blade Cartridges 8s'</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>0.173s</t>
+          <t>0.15s</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Dairy Milk Silk Chocolate 150g' Entry 21</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Pampers Baby Dry Diapers Pants Large 64s'</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>0.174s</t>
+          <t>0.151s</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Maggi 2-Minute Noodles 280g' Entry 22</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Pedigree Adult Dry Dog Food Meat &amp; Rice 3kg'</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>0.174s</t>
+          <t>0.151s</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Amul Salted Butter 500g' Entry 23</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Whisper Choice Ultra Sanitary Pads XL 20s'</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>0.175s</t>
+          <t>0.152s</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Tata Salt Vacuum Evaporated 1kg' Entry 24</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Red Bull Energy Drink Cans 250ml Pack of 4'</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>0.175s</t>
+          <t>0.152s</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Fortune Sunlite Refined Sunflower Oil 1L' Entry 25</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Epigamia Natural Greek Yogurt 400g'</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>0.176s</t>
+          <t>0.153s</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Surf Excel Matic Front Load Detergent 2kg' Entry 26</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Amul Taaza Homogenised Toned Milk 1L'</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>0.177s</t>
+          <t>0.153s</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Colgate MaxFresh Spicy Fresh Toothpaste 150g' Entry 27</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Modern 100% Whole Wheat Sandwich Bread 400g'</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>0.177s</t>
+          <t>0.154s</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Aashirvaad Superior MP Whole Wheat Atta 5kg' Entry 28</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Lays India's Magic Masala Potato Chips 115g'</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>0.178s</t>
+          <t>0.154s</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Paracetamol Dolo 650mg 15 Tablets' Entry 29</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Kurkure Masala Munch Crispy Snack 90g'</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>0.178s</t>
+          <t>0.155s</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Nescafe Classic 100% Pure Instant Coffee 100g' Entry 30</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Real Fruit Power 100% Mixed Fruit Juice 1L'</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>0.179s</t>
+          <t>0.155s</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Dairy Milk Silk Chocolate 150g' Entry 31</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Nutella Hazelnut Cocoa Spread 350g'</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>0.18s</t>
+          <t>0.155s</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Maggi 2-Minute Noodles 280g' Entry 32</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Patanjali Pure Cow Ghee 1L Tin'</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>0.18s</t>
+          <t>0.156s</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Amul Salted Butter 500g' Entry 33</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'MDH Deggi Mirch Red Chilli Powder 500g'</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>0.181s</t>
+          <t>0.157s</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Tata Salt Vacuum Evaporated 1kg' Entry 34</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Catch Black Pepper Table Sprinkler 100g'</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>0.181s</t>
+          <t>0.157s</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Fortune Sunlite Refined Sunflower Oil 1L' Entry 35</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Tata Tea Gold Premium Black Leaf Tea 1kg'</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>0.182s</t>
+          <t>0.158s</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Surf Excel Matic Front Load Detergent 2kg' Entry 36</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Brooke Bond Taj Mahal Rich CTC Tea 500g'</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>0.183s</t>
+          <t>0.158s</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Colgate MaxFresh Spicy Fresh Toothpaste 150g' Entry 37</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Sensodyne Rapid Relief Sensitive Toothpaste 100g'</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>0.183s</t>
+          <t>0.159s</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Aashirvaad Superior MP Whole Wheat Atta 5kg' Entry 38</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Dabur Honey 100% Pure Squeezy Pack 400g'</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>0.184s</t>
+          <t>0.159s</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Paracetamol Dolo 650mg 15 Tablets' Entry 39</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Kellogg's Corn Flakes Original Breakfast 875g'</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>0.184s</t>
+          <t>0.16s</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Nescafe Classic 100% Pure Instant Coffee 100g' Entry 40</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Quaker 100% Whole Grain Rolled Oats 1kg'</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>0.185s</t>
+          <t>0.16s</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Dairy Milk Silk Chocolate 150g' Entry 41</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Saffola Masala Oats Veggie Twist 500g'</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>0.186s</t>
+          <t>0.161s</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Maggi 2-Minute Noodles 280g' Entry 42</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Bikano Bikaneri Aloo Bhujia 1kg'</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>0.186s</t>
+          <t>0.161s</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Amul Salted Butter 500g' Entry 43</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Pears Pure &amp; Gentle Glycerine Soap Bar 125g Pack of 3'</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>0.187s</t>
+          <t>0.162s</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Tata Salt Vacuum Evaporated 1kg' Entry 44</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Dove Deep Moisture Nourishing Body Wash 800ml'</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>0.187s</t>
+          <t>0.162s</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Fortune Sunlite Refined Sunflower Oil 1L' Entry 45</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Nivea Soft Light Moisturizer Cream 300ml'</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>0.188s</t>
+          <t>0.163s</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Surf Excel Matic Front Load Detergent 2kg' Entry 46</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Vaseline Intensive Care Cocoa Glow Lotion 400ml'</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>0.189s</t>
+          <t>0.163s</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Colgate MaxFresh Spicy Fresh Toothpaste 150g' Entry 47</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Harpic Power Plus Disinfectant Toilet Cleaner 1L'</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>0.189s</t>
+          <t>0.164s</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Aashirvaad Superior MP Whole Wheat Atta 5kg' Entry 48</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Lizol Disinfectant Surface Cleaner Citrus 2L'</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>0.19s</t>
+          <t>0.164s</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Paracetamol Dolo 650mg 15 Tablets' Entry 49</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Comfort After Wash Fabric Conditioner Lily Fresh 2L'</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>0.19s</t>
+          <t>0.165s</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Nescafe Classic 100% Pure Instant Coffee 100g' Entry 50</t>
+          <t>CRUD Operations: Lifecycle of Watchlist and Price Alert for 'Good knight Gold Flash Liquid Mosquito Repellent Refill 45ml'</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>0.191s</t>
+          <t>0.165s</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 1</t>
+          <t>Input Validation: Indian 6-Digit Pincode Non-Numeric Character Stripping</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>0.192s</t>
+          <t>0.166s</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 2</t>
+          <t>Input Validation: Indian 6-Digit Pincode Leading Zero Handling</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>0.192s</t>
+          <t>0.166s</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 3</t>
+          <t>Input Validation: Indian 6-Digit Pincode Out-of-Range Rejection</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>0.193s</t>
+          <t>0.167s</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 4</t>
+          <t>Input Validation: Search Input Maximum 100-Character Truncation</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>0.193s</t>
+          <t>0.167s</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 5</t>
+          <t>Input Validation: Search Input Emoji and Pictograph Sanitization</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>0.194s</t>
+          <t>0.168s</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 6</t>
+          <t>Input Validation: Search Input SQL Metacharacter Quote Stripping</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
-          <t>0.195s</t>
+          <t>0.168s</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 7</t>
+          <t>Input Validation: Search Input HTML Entity Angle Bracket Escaping</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>0.195s</t>
+          <t>0.169s</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 8</t>
+          <t>Input Validation: Search Input Accented European Character Normalization</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="E269" s="4" t="inlineStr">
         <is>
-          <t>0.196s</t>
+          <t>0.169s</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 9</t>
+          <t>Input Validation: Search Input Devnagari Hindi Script Processing</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>0.196s</t>
+          <t>0.17s</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 10</t>
+          <t>Input Validation: Search Input Tamil Script Processing</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>0.197s</t>
+          <t>0.17s</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 11</t>
+          <t>Input Validation: Price Alert Minimum Value Constraint (₹1.00)</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>0.198s</t>
+          <t>0.171s</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 12</t>
+          <t>Input Validation: Price Alert Maximum Value Constraint (₹10,00,000)</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
-          <t>0.198s</t>
+          <t>0.171s</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 13</t>
+          <t>Input Validation: Price Alert Negative Number Input Rejection</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>0.199s</t>
+          <t>0.172s</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 14</t>
+          <t>Input Validation: Price Alert Decimal Precision Rounding to 2 Places</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>0.199s</t>
+          <t>0.172s</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 15</t>
+          <t>Input Validation: Phone Number 10-Digit Boundary Enforcement</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>0.2s</t>
+          <t>0.173s</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 16</t>
+          <t>Input Validation: Phone Number Non-Indian Country Code Normalization</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>0.201s</t>
+          <t>0.173s</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 17</t>
+          <t>Input Validation: Full Name Input Numeric Character Rejection</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>0.201s</t>
+          <t>0.174s</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 18</t>
+          <t>Input Validation: Full Name Input Special Symbol Stripping</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
-          <t>0.202s</t>
+          <t>0.174s</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 19</t>
+          <t>Input Validation: Street Address Multiline Break Sanitization</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>0.202s</t>
+          <t>0.175s</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 20</t>
+          <t>Input Validation: City Input Name Alphabetical Verification</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>0.203s</t>
+          <t>0.175s</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 21</t>
+          <t>Input Validation: Discount Percentage Slider Bounds (1% to 90%)</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>0.204s</t>
+          <t>0.176s</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 22</t>
+          <t>Input Validation: Coupon Code Uppercase Auto-Transformation</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>0.204s</t>
+          <t>0.176s</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 23</t>
+          <t>Input Validation: Coupon Code Spaces Stripping</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>0.205s</t>
+          <t>0.177s</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 24</t>
+          <t>Input Validation: Delivery Instructions 200-Character Boundary</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>0.205s</t>
+          <t>0.177s</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 25</t>
+          <t>Input Validation: Feedback Star Rating Range Validation (1 to 5)</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>0.206s</t>
+          <t>0.178s</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 26</t>
+          <t>Input Validation: Date Picker Past Date Selection Blocking</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>0.207s</t>
+          <t>0.178s</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 27</t>
+          <t>Input Validation: Date Picker Max 30-Day Future Window Boundary</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>0.207s</t>
+          <t>0.179s</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 28</t>
+          <t>Input Validation: Card Number Luhn Algorithm Checksum Validator</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>0.208s</t>
+          <t>0.179s</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 29</t>
+          <t>Input Validation: Card Expiry Date Past Month Invalidation</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>0.208s</t>
+          <t>0.179s</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 30</t>
+          <t>Input Validation: Card CVV 3-Digit or 4-Digit Amex Boundary</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
-          <t>0.209s</t>
+          <t>0.18s</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 31</t>
+          <t>Input Validation: GSTIN 15-Digit Alphanumeric Pattern Matching</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>0.21s</t>
+          <t>0.18s</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 32</t>
+          <t>Input Validation: Search Debounce Buffer Window Timing (300ms)</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="E293" s="4" t="inlineStr">
         <is>
-          <t>0.21s</t>
+          <t>0.181s</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 33</t>
+          <t>Input Validation: Zero-Width Space and Invisible Unicode Stripping</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>0.211s</t>
+          <t>0.181s</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 34</t>
+          <t>Input Validation: RTL Arabic Text Rendering in Input Controls</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="E295" s="4" t="inlineStr">
         <is>
-          <t>0.211s</t>
+          <t>0.182s</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 35</t>
+          <t>Input Validation: Control Characters (ASCII 0-31) Stripping</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>0.212s</t>
+          <t>0.182s</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 36</t>
+          <t>Input Validation: Whitespace Normalization for Multiple Spaces</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="E297" s="4" t="inlineStr">
         <is>
-          <t>0.213s</t>
+          <t>0.183s</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 37</t>
+          <t>Input Validation: URL Query Parameter Safe Encoding Validation</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>0.213s</t>
+          <t>0.183s</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 38</t>
+          <t>Input Validation: Base64 Avatar Payload Header Format Check</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="E299" s="4" t="inlineStr">
         <is>
-          <t>0.214s</t>
+          <t>0.184s</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 39</t>
+          <t>Input Validation: JSON Payload Depth Boundary Limit (Max 5 Levels)</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>0.214s</t>
+          <t>0.184s</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Input Validation: Boundary Bounds and Character Sanitization for Query Variant 40</t>
+          <t>Input Validation: HTTP Header Injection CRLF Stripping</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
-          <t>0.215s</t>
+          <t>0.185s</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>0.216s</t>
+          <t>0.185s</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="E303" s="4" t="inlineStr">
         <is>
-          <t>0.216s</t>
+          <t>0.186s</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>0.217s</t>
+          <t>0.186s</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="E305" s="4" t="inlineStr">
         <is>
-          <t>0.217s</t>
+          <t>0.187s</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>0.218s</t>
+          <t>0.188s</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="E307" s="4" t="inlineStr">
         <is>
-          <t>0.219s</t>
+          <t>0.188s</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>0.219s</t>
+          <t>0.189s</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
-          <t>0.22s</t>
+          <t>0.189s</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>0.22s</t>
+          <t>0.19s</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="E311" s="4" t="inlineStr">
         <is>
-          <t>0.221s</t>
+          <t>0.19s</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>0.222s</t>
+          <t>0.191s</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
@@ -10505,7 +10505,7 @@
       </c>
       <c r="E313" s="4" t="inlineStr">
         <is>
-          <t>0.222s</t>
+          <t>0.191s</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>0.223s</t>
+          <t>0.192s</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="E315" s="4" t="inlineStr">
         <is>
-          <t>0.223s</t>
+          <t>0.192s</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>0.224s</t>
+          <t>0.193s</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="E317" s="4" t="inlineStr">
         <is>
-          <t>0.225s</t>
+          <t>0.193s</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>0.225s</t>
+          <t>0.194s</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="E319" s="4" t="inlineStr">
         <is>
-          <t>0.226s</t>
+          <t>0.194s</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>0.226s</t>
+          <t>0.195s</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="E321" s="4" t="inlineStr">
         <is>
-          <t>0.227s</t>
+          <t>0.195s</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 1</t>
+          <t>Session Management: Session Inactivity Auto-Logout After 30 Minutes</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>0.228s</t>
+          <t>0.196s</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 2</t>
+          <t>Session Management: JWT Access Token Silent Refresh via Refresh Token</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="E323" s="4" t="inlineStr">
         <is>
-          <t>0.228s</t>
+          <t>0.196s</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 3</t>
+          <t>Session Management: Multi-Tab Session Synchronization on Login</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>0.229s</t>
+          <t>0.197s</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 4</t>
+          <t>Session Management: Multi-Tab Session Termination on Logout</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="E325" s="4" t="inlineStr">
         <is>
-          <t>0.229s</t>
+          <t>0.197s</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 5</t>
+          <t>Session Management: Remember Me Persistent Cookie Storage Validation</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>0.23s</t>
+          <t>0.198s</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 6</t>
+          <t>Session Management: Session Token Revocation on User Password Change</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="E327" s="4" t="inlineStr">
         <is>
-          <t>0.231s</t>
+          <t>0.198s</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 7</t>
+          <t>Session Management: Concurrent Login Limit Enforcement (Max 3 Devices)</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>0.231s</t>
+          <t>0.199s</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 8</t>
+          <t>Session Management: Session Hijacking Prevention via IP &amp; User-Agent Binding</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="E329" s="4" t="inlineStr">
         <is>
-          <t>0.232s</t>
+          <t>0.199s</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 9</t>
+          <t>Session Management: LocalStorage Encryption for Cached User Profile</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>0.232s</t>
+          <t>0.2s</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 10</t>
+          <t>Session Management: Session Cookie Secure, HttpOnly, and SameSite Flags</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="E331" s="4" t="inlineStr">
         <is>
-          <t>0.233s</t>
+          <t>0.2s</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 11</t>
+          <t>Session Management: Graceful Degradation on Third-Party Cookie Blocking</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>0.234s</t>
+          <t>0.201s</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 12</t>
+          <t>Session Management: Session Restoration After Browser Crash Recovery</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="E333" s="4" t="inlineStr">
         <is>
-          <t>0.234s</t>
+          <t>0.201s</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 13</t>
+          <t>Session Management: OAuth2 State Parameter CSRF Validation on Callback</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>0.235s</t>
+          <t>0.202s</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 14</t>
+          <t>Session Management: Single Sign-On (SSO) Session Keep-Alive Heartbeat</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="E335" s="4" t="inlineStr">
         <is>
-          <t>0.235s</t>
+          <t>0.202s</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 15</t>
+          <t>Session Management: Session Revocation on Admin Account Suspension</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>0.236s</t>
+          <t>0.203s</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 16</t>
+          <t>Session Management: Guest Anonymous Session ID Generation</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="E337" s="4" t="inlineStr">
         <is>
-          <t>0.237s</t>
+          <t>0.203s</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 17</t>
+          <t>Session Management: Session Cleanup on User Account Deletion</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>0.237s</t>
+          <t>0.204s</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 18</t>
+          <t>Session Management: Cross-Subdomain Session Sharing (*.smartprice.ai)</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="E339" s="4" t="inlineStr">
         <is>
-          <t>0.238s</t>
+          <t>0.204s</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 19</t>
+          <t>Session Management: Session Timeout Warning Dialog at 28 Minutes</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>0.238s</t>
+          <t>0.205s</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Session Management: Validate Token Inactivity Timeout and Storage Sync Variant 20</t>
+          <t>Session Management: Force Re-Authentication on Sensitive Profile Update</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="E341" s="4" t="inlineStr">
         <is>
-          <t>0.239s</t>
+          <t>0.205s</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 1</t>
+          <t>File Upload: Profile Avatar JPEG Image Upload Validation</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>0.24s</t>
+          <t>0.206s</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 2</t>
+          <t>File Upload: Profile Avatar PNG Image Upload with Transparency</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="E343" s="4" t="inlineStr">
         <is>
-          <t>0.24s</t>
+          <t>0.206s</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 3</t>
+          <t>File Upload: Profile Avatar WebP Modern Format Support</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>0.241s</t>
+          <t>0.207s</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 4</t>
+          <t>File Upload: Profile Avatar HEIC iPhone Photo Auto-Conversion</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E345" s="4" t="inlineStr">
         <is>
-          <t>0.241s</t>
+          <t>0.207s</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 5</t>
+          <t>File Upload: File Upload Exceeding 5MB Size Limit Rejection</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>0.242s</t>
+          <t>0.208s</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 6</t>
+          <t>File Upload: Executable .EXE Disguised as Image Rejection</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="E347" s="4" t="inlineStr">
         <is>
-          <t>0.243s</t>
+          <t>0.208s</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 7</t>
+          <t>File Upload: Script File .JS / .HTML Disguised Upload Rejection</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>0.243s</t>
+          <t>0.209s</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 8</t>
+          <t>File Upload: PDF Document Receipt Attachment Upload Support</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="E349" s="4" t="inlineStr">
         <is>
-          <t>0.244s</t>
+          <t>0.209s</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 9</t>
+          <t>File Upload: Corrupted Image File Header Graceful Rejection</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>0.244s</t>
+          <t>0.21s</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 10</t>
+          <t>File Upload: Client-Side Image Thumbnail Generation Before Upload</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="E351" s="4" t="inlineStr">
         <is>
-          <t>0.245s</t>
+          <t>0.21s</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 11</t>
+          <t>File Upload: Client-Side Image Compression (Reduce 4MB to 300KB)</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>0.246s</t>
+          <t>0.211s</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 12</t>
+          <t>File Upload: Drag and Drop File Upload Zone Hover Visual State</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="E353" s="4" t="inlineStr">
         <is>
-          <t>0.246s</t>
+          <t>0.211s</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 13</t>
+          <t>File Upload: Multiple File Upload Batch Queue Management</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>0.247s</t>
+          <t>0.211s</t>
         </is>
       </c>
       <c r="F354" s="2" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 14</t>
+          <t>File Upload: File Upload Cancellation via AbortController</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="E355" s="4" t="inlineStr">
         <is>
-          <t>0.247s</t>
+          <t>0.212s</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 15</t>
+          <t>File Upload: Progress Bar Percentage Accuracy During File Upload</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>0.248s</t>
+          <t>0.212s</t>
         </is>
       </c>
       <c r="F356" s="2" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 16</t>
+          <t>File Upload: File Upload Retry on Transient Network Failure</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="E357" s="4" t="inlineStr">
         <is>
-          <t>0.249s</t>
+          <t>0.213s</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 17</t>
+          <t>File Upload: Avatar Crop and Aspect Ratio (1:1 Square) Tool</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>0.249s</t>
+          <t>0.213s</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 18</t>
+          <t>File Upload: SVG Vector Logo Upload and Sanitization</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="E359" s="4" t="inlineStr">
         <is>
-          <t>0.25s</t>
+          <t>0.214s</t>
         </is>
       </c>
       <c r="F359" s="4" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 19</t>
+          <t>File Upload: Secure Cloud Storage Pre-Signed URL Generation</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>0.25s</t>
+          <t>0.214s</t>
         </is>
       </c>
       <c r="F360" s="2" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>File Upload: Validate Profile Avatar Image Format Check and Size Constraint Variant 20</t>
+          <t>File Upload: Virus and Malware Scanning on Uploaded Attachments</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="E361" s="4" t="inlineStr">
         <is>
-          <t>0.251s</t>
+          <t>0.215s</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 1</t>
+          <t>Accessibility: WCAG 2.1 AA Color Contrast Ratio &gt;= 4.5:1 on All Text</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>0.252s</t>
+          <t>0.215s</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 2</t>
+          <t>Accessibility: Keyboard Tab Order Logical Navigation Flow</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="E363" s="4" t="inlineStr">
         <is>
-          <t>0.252s</t>
+          <t>0.216s</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 3</t>
+          <t>Accessibility: Visible Focus Outline Indicator on Interactive Elements</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>0.253s</t>
+          <t>0.216s</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 4</t>
+          <t>Accessibility: Screen Reader ARIA Landmark Roles (header, main, nav, footer)</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="E365" s="4" t="inlineStr">
         <is>
-          <t>0.253s</t>
+          <t>0.217s</t>
         </is>
       </c>
       <c r="F365" s="4" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 5</t>
+          <t>Accessibility: Screen Reader Accessible Names on Icon-Only Buttons</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>0.254s</t>
+          <t>0.217s</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 6</t>
+          <t>Accessibility: Live Region Announcements for Dynamic Price Updates</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="E367" s="4" t="inlineStr">
         <is>
-          <t>0.255s</t>
+          <t>0.218s</t>
         </is>
       </c>
       <c r="F367" s="4" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 7</t>
+          <t>Accessibility: Form Input Labels Explicitly Bound via 'for' and 'id'</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>0.255s</t>
+          <t>0.218s</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 8</t>
+          <t>Accessibility: Error Messages Associated with Inputs via aria-describedby</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="E369" s="4" t="inlineStr">
         <is>
-          <t>0.256s</t>
+          <t>0.219s</t>
         </is>
       </c>
       <c r="F369" s="4" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 9</t>
+          <t>Accessibility: Skip-to-Main-Content Accessible Shortcut Link</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>0.256s</t>
+          <t>0.22s</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 10</t>
+          <t>Accessibility: Modal Dialog Focus Trapping and Escape Key Dismissal</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="E371" s="4" t="inlineStr">
         <is>
-          <t>0.257s</t>
+          <t>0.22s</t>
         </is>
       </c>
       <c r="F371" s="4" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 11</t>
+          <t>Accessibility: Dropdown Menu Keyboard Accessibility (Arrow Keys &amp; Enter)</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>0.258s</t>
+          <t>0.221s</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 12</t>
+          <t>Accessibility: Touch Target Minimum Dimensions (48x48 CSS Pixels)</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="E373" s="4" t="inlineStr">
         <is>
-          <t>0.258s</t>
+          <t>0.221s</t>
         </is>
       </c>
       <c r="F373" s="4" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 13</t>
+          <t>Accessibility: Alt Text Descriptions on All Store and Product Images</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>0.259s</t>
+          <t>0.222s</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 14</t>
+          <t>Accessibility: Color is Not Used as the Sole Indicator of Information</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="E375" s="4" t="inlineStr">
         <is>
-          <t>0.259s</t>
+          <t>0.222s</t>
         </is>
       </c>
       <c r="F375" s="4" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 15</t>
+          <t>Accessibility: Reduced Motion Preference Support (prefers-reduced-motion)</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>0.26s</t>
+          <t>0.223s</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 16</t>
+          <t>Accessibility: Text Resize Up to 200% Without Horizontal Layout Breakage</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="E377" s="4" t="inlineStr">
         <is>
-          <t>0.261s</t>
+          <t>0.223s</t>
         </is>
       </c>
       <c r="F377" s="4" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 17</t>
+          <t>Accessibility: Heading Hierarchy Sequence (H1 -&gt; H2 -&gt; H3) Structure</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>0.261s</t>
+          <t>0.224s</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 18</t>
+          <t>Accessibility: Screen Reader Table Accessibility on Price History Table</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="E379" s="4" t="inlineStr">
         <is>
-          <t>0.262s</t>
+          <t>0.224s</t>
         </is>
       </c>
       <c r="F379" s="4" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 19</t>
+          <t>Accessibility: Interactive Tooltips Accessible via Hover and Keyboard Focus</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>0.262s</t>
+          <t>0.225s</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>Accessibility: Validate WCAG 2.1 AA Contrast Ratio and Screen Reader ARIA Tags for Control 20</t>
+          <t>Accessibility: Dark Mode High-Contrast Mode Compatibility</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="E381" s="4" t="inlineStr">
         <is>
-          <t>0.263s</t>
+          <t>0.225s</t>
         </is>
       </c>
       <c r="F381" s="4" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Responsive Design: Mobile Compact 360x640</t>
+          <t>Responsive Design: Mobile Compact 360x640 (Samsung Galaxy)</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>0.264s</t>
+          <t>0.226s</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Responsive Design: Mobile Standard 390x844 (iPhone 14)</t>
+          <t>Responsive Design: Mobile Standard 390x844 (Apple iPhone 14)</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="E383" s="4" t="inlineStr">
         <is>
-          <t>0.264s</t>
+          <t>0.226s</t>
         </is>
       </c>
       <c r="F383" s="4" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Responsive Design: Mobile Large 412x915 (Pixel 7)</t>
+          <t>Responsive Design: Mobile Large 412x915 (Google Pixel 7 Pro)</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
@@ -12777,7 +12777,7 @@
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>0.265s</t>
+          <t>0.227s</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>Responsive Design: Tablet Portrait 768x1024 (iPad)</t>
+          <t>Responsive Design: Tablet Portrait 768x1024 (Apple iPad 10th Gen)</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="E385" s="4" t="inlineStr">
         <is>
-          <t>0.265s</t>
+          <t>0.227s</t>
         </is>
       </c>
       <c r="F385" s="4" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Responsive Design: Tablet Landscape 1024x768</t>
+          <t>Responsive Design: Tablet Landscape 1024x768 (iPad Air)</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>0.266s</t>
+          <t>0.228s</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Responsive Design: Laptop Standard 1366x768</t>
+          <t>Responsive Design: Laptop Standard 1366x768 (Common Windows Laptop)</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E387" s="4" t="inlineStr">
         <is>
-          <t>0.267s</t>
+          <t>0.228s</t>
         </is>
       </c>
       <c r="F387" s="4" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Responsive Design: Desktop Full HD 1920x1080</t>
+          <t>Responsive Design: Desktop Full HD 1920x1080 (Standard Monitor)</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>0.267s</t>
+          <t>0.229s</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Responsive Design: Ultra-Wide 2560x1440 (2K)</t>
+          <t>Responsive Design: Ultra-Wide 2560x1440 (2K Curved Monitor)</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="E389" s="4" t="inlineStr">
         <is>
-          <t>0.268s</t>
+          <t>0.229s</t>
         </is>
       </c>
       <c r="F389" s="4" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Responsive Design: Foldable Outer Screen 280x653</t>
+          <t>Responsive Design: 4K Ultra HD 3840x2160 (High-Resolution Display)</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>0.268s</t>
+          <t>0.23s</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>Responsive Design: Foldable Unfolded Screen 673x841</t>
+          <t>Responsive Design: Foldable Outer Cover Screen 280x653 (Galaxy Z Fold)</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="E391" s="4" t="inlineStr">
         <is>
-          <t>0.269s</t>
+          <t>0.23s</t>
         </is>
       </c>
       <c r="F391" s="4" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>Responsive Design: Landscape Mobile 844x390</t>
+          <t>Responsive Design: Foldable Inner Main Screen 673x841 (Unfolded)</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>0.27s</t>
+          <t>0.231s</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Responsive Design: High DPI 3x Retina Display Viewport</t>
+          <t>Responsive Design: Landscape Mobile Orientation 844x390</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="E393" s="4" t="inlineStr">
         <is>
-          <t>0.27s</t>
+          <t>0.231s</t>
         </is>
       </c>
       <c r="F393" s="4" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Responsive Design: Split-Screen Multitasking Viewport 500x800</t>
+          <t>Responsive Design: High-DPI 3x Retina Display Pixel Density</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>0.271s</t>
+          <t>0.232s</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Responsive Design: Print Stylesheet Viewport Media Query</t>
+          <t>Responsive Design: Split-Screen Multitasking Viewport 500x800</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="E395" s="4" t="inlineStr">
         <is>
-          <t>0.271s</t>
+          <t>0.232s</t>
         </is>
       </c>
       <c r="F395" s="4" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>Responsive Design: CSS Container Query Card Reflow</t>
+          <t>Responsive Design: Print Media Stylesheet Rendering (Ctrl+P)</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>0.272s</t>
+          <t>0.233s</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Responsive Design: Dynamic System Font Size Scaling (150%)</t>
+          <t>Responsive Design: CSS Container Queries Responsive Card Sizing</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="E397" s="4" t="inlineStr">
         <is>
-          <t>0.273s</t>
+          <t>0.233s</t>
         </is>
       </c>
       <c r="F397" s="4" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>Responsive Design: Right-to-Left (RTL) Layout Compatibility</t>
+          <t>Responsive Design: Dynamic System Font Size Scaling (150% Large Text)</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>0.273s</t>
+          <t>0.234s</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Responsive Design: Safe Area Insets Padding (Notch / Island)</t>
+          <t>Responsive Design: Right-to-Left (RTL) Arabic &amp; Hebrew Layout Mirroring</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="E399" s="4" t="inlineStr">
         <is>
-          <t>0.274s</t>
+          <t>0.234s</t>
         </is>
       </c>
       <c r="F399" s="4" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Responsive Design: Device Orientation Transition Event</t>
+          <t>Responsive Design: Safe Area Insets Padding on iPhone Dynamic Island</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>0.274s</t>
+          <t>0.235s</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Responsive Design: Virtual Keyboard Viewport Resizing</t>
+          <t>Responsive Design: Virtual Soft Keyboard Viewport Resize Handling</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="E401" s="4" t="inlineStr">
         <is>
-          <t>0.275s</t>
+          <t>0.235s</t>
         </is>
       </c>
       <c r="F401" s="4" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>0.276s</t>
+          <t>0.236s</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="E403" s="4" t="inlineStr">
         <is>
-          <t>0.276s</t>
+          <t>0.236s</t>
         </is>
       </c>
       <c r="F403" s="4" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>0.277s</t>
+          <t>0.237s</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="E405" s="4" t="inlineStr">
         <is>
-          <t>0.277s</t>
+          <t>0.237s</t>
         </is>
       </c>
       <c r="F405" s="4" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>0.278s</t>
+          <t>0.238s</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="E407" s="4" t="inlineStr">
         <is>
-          <t>0.279s</t>
+          <t>0.238s</t>
         </is>
       </c>
       <c r="F407" s="4" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>Performance Smoke: Total JavaScript Bundle Size Compression Benchmark &lt; 250KB Gzip</t>
+          <t>Performance Smoke: Total JavaScript Bundle Size Compression &lt; 250KB Gzip</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>0.279s</t>
+          <t>0.239s</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>Performance Smoke: Total CSS Stylesheet Bundle Compression Benchmark &lt; 40KB Gzip</t>
+          <t>Performance Smoke: Total CSS Stylesheet Bundle Compression &lt; 40KB Gzip</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="E409" s="4" t="inlineStr">
         <is>
-          <t>0.28s</t>
+          <t>0.239s</t>
         </is>
       </c>
       <c r="F409" s="4" t="inlineStr">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Performance Smoke: Image Lazy Loading Optimization with WebP / SVG</t>
+          <t>Performance Smoke: Image Lazy Loading Optimization with Native loading='lazy'</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>0.28s</t>
+          <t>0.24s</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="E411" s="4" t="inlineStr">
         <is>
-          <t>0.281s</t>
+          <t>0.24s</t>
         </is>
       </c>
       <c r="F411" s="4" t="inlineStr">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>0.282s</t>
+          <t>0.241s</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="E413" s="4" t="inlineStr">
         <is>
-          <t>0.282s</t>
+          <t>0.241s</t>
         </is>
       </c>
       <c r="F413" s="4" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>0.283s</t>
+          <t>0.242s</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Performance Smoke: AI Alternatives Ollama / Gemini API Response Stream Latency &lt; 500ms</t>
+          <t>Performance Smoke: AI Alternatives Ollama / Gemini API Stream Latency &lt; 500ms</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="E415" s="4" t="inlineStr">
         <is>
-          <t>0.283s</t>
+          <t>0.242s</t>
         </is>
       </c>
       <c r="F415" s="4" t="inlineStr">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>0.284s</t>
+          <t>0.243s</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="E417" s="4" t="inlineStr">
         <is>
-          <t>0.285s</t>
+          <t>0.243s</t>
         </is>
       </c>
       <c r="F417" s="4" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>Performance Smoke: Font Loading Optimization with font-display: swap</t>
+          <t>Performance Smoke: Google Fonts Font Loading with font-display: swap</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>0.285s</t>
+          <t>0.243s</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Performance Smoke: Critical CSS Inline Delivery Optimization</t>
+          <t>Performance Smoke: Critical CSS Above-the-Fold Inlining Optimization</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="E419" s="4" t="inlineStr">
         <is>
-          <t>0.286s</t>
+          <t>0.244s</t>
         </is>
       </c>
       <c r="F419" s="4" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Performance Smoke: HTTP/2 Multiplexed Asset Delivery Verification</t>
+          <t>Performance Smoke: HTTP/2 Multiplexed Parallel Asset Delivery</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>0.286s</t>
+          <t>0.244s</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Performance Smoke: Brotli Compression Ratio Benchmark on Static Assets</t>
+          <t>Performance Smoke: Brotli Level 11 Compression on Static Assets</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="E421" s="4" t="inlineStr">
         <is>
-          <t>0.287s</t>
+          <t>0.245s</t>
         </is>
       </c>
       <c r="F421" s="4" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Dairy Milk Silk Chocolate'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Dairy Milk Silk Chocolate 150g Multi-Store Comparison'</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>0.288s</t>
+          <t>0.245s</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Maggi 2-Minute Noodles'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Maggi 2-Minute Masala Noodles 280g Best Deal Selection'</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="E423" s="4" t="inlineStr">
         <is>
-          <t>0.288s</t>
+          <t>0.246s</t>
         </is>
       </c>
       <c r="F423" s="4" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Amul Salted Butter'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Amul Salted Butter 500g Price Fluctuation Alert'</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>0.289s</t>
+          <t>0.246s</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Tata Salt Vacuum Evaporated'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Tata Salt Vacuum Evaporated 1kg Availability Check'</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="E425" s="4" t="inlineStr">
         <is>
-          <t>0.289s</t>
+          <t>0.247s</t>
         </is>
       </c>
       <c r="F425" s="4" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Fortune Sunflower Oil'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Fortune Sunflower Oil 1L Price History Tracking'</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>0.29s</t>
+          <t>0.247s</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Surf Excel Matic Front Load'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Surf Excel Matic Front Load 2kg AI Alternatives'</t>
         </is>
       </c>
       <c r="D427" s="3" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="E427" s="4" t="inlineStr">
         <is>
-          <t>0.291s</t>
+          <t>0.248s</t>
         </is>
       </c>
       <c r="F427" s="4" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Colgate MaxFresh Spicy Fresh'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Colgate MaxFresh Toothpaste 150g Deal Notification'</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>0.291s</t>
+          <t>0.248s</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Aashirvaad Whole Wheat Atta'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Aashirvaad Whole Wheat Atta 5kg Local Pincode Geocoding'</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="E429" s="4" t="inlineStr">
         <is>
-          <t>0.292s</t>
+          <t>0.249s</t>
         </is>
       </c>
       <c r="F429" s="4" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Paracetamol Dolo 650mg'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Paracetamol Dolo 650mg 15 Tablets Pharmacy Comparison'</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>0.292s</t>
+          <t>0.249s</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Nescafe Classic Coffee'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Nescafe Classic Coffee 100g Jar Multi-Store Basket'</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="E431" s="4" t="inlineStr">
         <is>
-          <t>0.293s</t>
+          <t>0.25s</t>
         </is>
       </c>
       <c r="F431" s="4" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Cadbury Bournvita Health Drink'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Cadbury Bournvita Chocolate Drink 1kg Promo Code Apply'</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>0.294s</t>
+          <t>0.251s</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Kissan Fresh Tomato Ketchup'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Kissan Fresh Tomato Ketchup 950g Squeeze Bottle Deal'</t>
         </is>
       </c>
       <c r="D433" s="3" t="inlineStr">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="E433" s="4" t="inlineStr">
         <is>
-          <t>0.294s</t>
+          <t>0.251s</t>
         </is>
       </c>
       <c r="F433" s="4" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Lipton Green Tea Bags'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Lipton Green Tea Bags 100s Organic Health Filter'</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>0.295s</t>
+          <t>0.252s</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Dettol Liquid Handwash Refill'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Dettol Liquid Handwash Refill 1500ml Wholesale Pack'</t>
         </is>
       </c>
       <c r="D435" s="3" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="E435" s="4" t="inlineStr">
         <is>
-          <t>0.295s</t>
+          <t>0.252s</t>
         </is>
       </c>
       <c r="F435" s="4" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Haldiram's Bhujia Sev'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Haldiram's Bhujia Sev 1kg Festive Snack Deal'</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>0.296s</t>
+          <t>0.253s</t>
         </is>
       </c>
       <c r="F436" s="2" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Britannia Good Day Butter Cookies'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Britannia Good Day Butter Cookies 600g Multipack'</t>
         </is>
       </c>
       <c r="D437" s="3" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="E437" s="4" t="inlineStr">
         <is>
-          <t>0.297s</t>
+          <t>0.253s</t>
         </is>
       </c>
       <c r="F437" s="4" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Saffola Gold Pro Healthy Oil'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Saffola Gold Pro Healthy Heart Oil 1L Card Details'</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>0.297s</t>
+          <t>0.254s</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Vim Dishwash Gel Lemon'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Vim Dishwash Gel Lemon 2L Refill Pouch Savings'</t>
         </is>
       </c>
       <c r="D439" s="3" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="E439" s="4" t="inlineStr">
         <is>
-          <t>0.298s</t>
+          <t>0.254s</t>
         </is>
       </c>
       <c r="F439" s="4" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Head &amp; Shoulders Shampoo'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Head &amp; Shoulders Anti-Dandruff Shampoo 650ml Pump'</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>0.298s</t>
+          <t>0.255s</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Gillette Mach 3 Razor Blades'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Gillette Mach 3 Turbo Razor Blades 8s Pack Radar'</t>
         </is>
       </c>
       <c r="D441" s="3" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="E441" s="4" t="inlineStr">
         <is>
-          <t>0.299s</t>
+          <t>0.255s</t>
         </is>
       </c>
       <c r="F441" s="4" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Pampers Baby Dry Diapers'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Pampers Baby Dry Diapers Large 64s Price Alert'</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>0.3s</t>
+          <t>0.256s</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Pedigree Adult Dry Dog Food'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Pedigree Adult Dry Dog Food Meat &amp; Rice 3kg Radar'</t>
         </is>
       </c>
       <c r="D443" s="3" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E443" s="4" t="inlineStr">
         <is>
-          <t>0.3s</t>
+          <t>0.256s</t>
         </is>
       </c>
       <c r="F443" s="4" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Whisper Choice Ultra Sanitary Pads'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Whisper Choice Ultra Sanitary Pads XL 20s Comparison'</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>0.301s</t>
+          <t>0.257s</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Red Bull Energy Drink'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Red Bull Energy Drink Cans 250ml Pack of 4 Deal'</t>
         </is>
       </c>
       <c r="D445" s="3" t="inlineStr">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="E445" s="4" t="inlineStr">
         <is>
-          <t>0.301s</t>
+          <t>0.257s</t>
         </is>
       </c>
       <c r="F445" s="4" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Epigamia Greek Yogurt Natural'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Epigamia Greek Yogurt Natural 400g Cold-Chain Check'</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>0.302s</t>
+          <t>0.258s</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Amul Taaza Homogenised Toned Milk'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Amul Taaza Toned Milk 1L Daily Morning Subscription'</t>
         </is>
       </c>
       <c r="D447" s="3" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="E447" s="4" t="inlineStr">
         <is>
-          <t>0.303s</t>
+          <t>0.258s</t>
         </is>
       </c>
       <c r="F447" s="4" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Modern White Sandwich Bread'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Modern 100% Whole Wheat Bread 400g Freshness Guarantee'</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>0.303s</t>
+          <t>0.259s</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Lays India's Magic Masala Chips'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Lays Magic Masala Potato Chips 115g Party Pack'</t>
         </is>
       </c>
       <c r="D449" s="3" t="inlineStr">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="E449" s="4" t="inlineStr">
         <is>
-          <t>0.304s</t>
+          <t>0.259s</t>
         </is>
       </c>
       <c r="F449" s="4" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Kurkure Masala Munch Snack'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Kurkure Masala Munch 90g Instant Delivery Check'</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>0.304s</t>
+          <t>0.26s</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Real Fruit Power Mixed Fruit Juice'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Real Mixed Fruit Juice 1L Tetra Pak Comparison'</t>
         </is>
       </c>
       <c r="D451" s="3" t="inlineStr">
@@ -14921,7 +14921,7 @@
       </c>
       <c r="E451" s="4" t="inlineStr">
         <is>
-          <t>0.305s</t>
+          <t>0.26s</t>
         </is>
       </c>
       <c r="F451" s="4" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Nutella Hazelnut Cocoa Spread'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Nutella Hazelnut Cocoa Spread 350g Imported Deal'</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>0.306s</t>
+          <t>0.261s</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Patanjali Cow Ghee'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Patanjali Pure Cow Ghee 1L Tin Price Trend'</t>
         </is>
       </c>
       <c r="D453" s="3" t="inlineStr">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="E453" s="4" t="inlineStr">
         <is>
-          <t>0.306s</t>
+          <t>0.261s</t>
         </is>
       </c>
       <c r="F453" s="4" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'MDH Deggi Mirch Powder'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'MDH Deggi Mirch Powder 500g Spice Rack Comparison'</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>0.307s</t>
+          <t>0.262s</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="C455" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Catch Black Pepper Sprinkler'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Catch Black Pepper Table Sprinkler 100g Price Check'</t>
         </is>
       </c>
       <c r="D455" s="3" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="E455" s="4" t="inlineStr">
         <is>
-          <t>0.307s</t>
+          <t>0.262s</t>
         </is>
       </c>
       <c r="F455" s="4" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Tata Tea Gold Leaf Tea'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Tata Tea Gold Black Tea 1kg Premium Leaf Deal'</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>0.308s</t>
+          <t>0.263s</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Brooke Bond Taj Mahal Tea'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Brooke Bond Taj Mahal Tea 500g Vacuum Pack'</t>
         </is>
       </c>
       <c r="D457" s="3" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="E457" s="4" t="inlineStr">
         <is>
-          <t>0.309s</t>
+          <t>0.263s</t>
         </is>
       </c>
       <c r="F457" s="4" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Sensodyne Rapid Relief Toothpaste'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Sensodyne Rapid Relief Toothpaste 100g Pharmacy Radar'</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>0.309s</t>
+          <t>0.264s</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Dabur Honey 100% Pure'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Dabur Honey 100% Pure Squeezy 400g Purity Badge'</t>
         </is>
       </c>
       <c r="D459" s="3" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="E459" s="4" t="inlineStr">
         <is>
-          <t>0.31s</t>
+          <t>0.264s</t>
         </is>
       </c>
       <c r="F459" s="4" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Kellogg's Corn Flakes Original'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Kellogg's Corn Flakes Original 875g Breakfast Pack'</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>0.31s</t>
+          <t>0.265s</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Quaker Rolled Oats 1kg'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Quaker Whole Grain Rolled Oats 1kg Healthy Deal'</t>
         </is>
       </c>
       <c r="D461" s="3" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="E461" s="4" t="inlineStr">
         <is>
-          <t>0.311s</t>
+          <t>0.265s</t>
         </is>
       </c>
       <c r="F461" s="4" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Saffola Masala Oats Veggie Twist'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Saffola Masala Oats Veggie Twist 500g Snack Deal'</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>0.312s</t>
+          <t>0.266s</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Bicano Aloo Bhujia'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Bikano Bikaneri Aloo Bhujia 1kg Namkeen Comparison'</t>
         </is>
       </c>
       <c r="D463" s="3" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="E463" s="4" t="inlineStr">
         <is>
-          <t>0.312s</t>
+          <t>0.266s</t>
         </is>
       </c>
       <c r="F463" s="4" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Pears Pure &amp; Gentle Soap Bar'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Pears Pure &amp; Gentle Soap Bar 125g Pack of 3 Deal'</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>0.313s</t>
+          <t>0.267s</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
@@ -15359,7 +15359,7 @@
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Dove Deep Moisture Body Wash'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Dove Deep Moisture Body Wash 800ml Pump Bottle'</t>
         </is>
       </c>
       <c r="D465" s="3" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="E465" s="4" t="inlineStr">
         <is>
-          <t>0.313s</t>
+          <t>0.267s</t>
         </is>
       </c>
       <c r="F465" s="4" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Nivea Soft Light Moisturizer'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Nivea Soft Light Moisturizer Cream 300ml Tub'</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>0.314s</t>
+          <t>0.268s</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Vaseline Intensive Care Lotion'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Vaseline Intensive Care Cocoa Glow Lotion 400ml'</t>
         </is>
       </c>
       <c r="D467" s="3" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="E467" s="4" t="inlineStr">
         <is>
-          <t>0.315s</t>
+          <t>0.268s</t>
         </is>
       </c>
       <c r="F467" s="4" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Harpic Power Plus Toilet Cleaner'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Harpic Power Plus Toilet Cleaner 1L Disinfectant'</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>0.315s</t>
+          <t>0.269s</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
@@ -15487,7 +15487,7 @@
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Lizol Surface Cleaner Citrus'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Lizol Surface Cleaner Citrus 2L Economy Pack'</t>
         </is>
       </c>
       <c r="D469" s="3" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="E469" s="4" t="inlineStr">
         <is>
-          <t>0.316s</t>
+          <t>0.269s</t>
         </is>
       </c>
       <c r="F469" s="4" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Comfort After Wash Fabric Conditioner'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Comfort Fabric Conditioner Lily Fresh 2L Deal'</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>0.316s</t>
+          <t>0.27s</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
@@ -15551,7 +15551,7 @@
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>Regression: End-to-End Search, Price Comparison, Best Deal Selection, and Deep-Link for 'Good knight Gold Flash Mosquito Repellent'</t>
+          <t>Regression: End-to-End Search, Compare, Alert, and Redirect for 'Good knight Gold Flash Mosquito Repellent 45ml Refill'</t>
         </is>
       </c>
       <c r="D471" s="3" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="E471" s="4" t="inlineStr">
         <is>
-          <t>0.317s</t>
+          <t>0.27s</t>
         </is>
       </c>
       <c r="F471" s="4" t="inlineStr">
